--- a/resource/table/base_sentences.xlsx
+++ b/resource/table/base_sentences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09B9FFE-6412-43C2-9853-7EA928D64FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BADCAAA-E2CE-4C0E-9427-069FE2701B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -120,13 +120,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>video_end_ms</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>video_start_ms</t>
-  </si>
-  <si>
     <t>video_path</t>
   </si>
   <si>
@@ -142,9 +135,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>resource/video/fruit_store/1.mp4</t>
-  </si>
-  <si>
     <t>resource/sound/fruit_store/1_1.mp3</t>
   </si>
   <si>
@@ -282,10 +272,6 @@
   </si>
   <si>
     <t>resource/sound/fruit_store/4_1.mp3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>resource/video/fruit_store/10.mp4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -461,6 +447,60 @@
   </si>
   <si>
     <t>要(필요하다)\n중국의 근은 500g\n중국은 과일을 무게(근)로 판매함</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/fruit_store/我要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>两斤草莓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/fruit_store/苹果多少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1038,9 +1078,9 @@
     <col min="2" max="2" width="3.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="87" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="36.75" bestFit="1" customWidth="1"/>
@@ -1058,25 +1098,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="M1" s="4"/>
       <c r="O1" s="4"/>
@@ -1095,19 +1129,13 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5">
-        <v>3749</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>23</v>
       </c>
       <c r="L2" s="13"/>
       <c r="M2" s="13"/>
@@ -1121,56 +1149,44 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
         <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1360</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
       </c>
       <c r="M3" s="13"/>
       <c r="N3" s="13"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
-        <v>3749</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>23</v>
+      <c r="G4" s="15" t="s">
+        <v>19</v>
       </c>
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
@@ -1178,31 +1194,25 @@
     </row>
     <row r="5" spans="1:15" ht="18.75">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
-        <v>3749</v>
-      </c>
-      <c r="H5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="13"/>

--- a/resource/table/base_sentences.xlsx
+++ b/resource/table/base_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BADCAAA-E2CE-4C0E-9427-069FE2701B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FC827B-2849-48A6-BCD7-EAE56EAEFA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="7035" yWindow="4110" windowWidth="27180" windowHeight="10935" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -501,6 +501,802 @@
       </rPr>
       <t>.mp4</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>shi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>당신은 회사원인가요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>上班族</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{我}{是}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>毕业</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>生}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/shi/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>你是上班族吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/shi/我是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>毕业生</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>你是上班族吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/我是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>毕业生</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 졸업생이에요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>是 : ~이다 (영어의 be 동사와 유사)\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> : 문장 끝에 붙여 의문문을 만듦</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是 : ~이다 (영어의 be 동사와 유사)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>locatives</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{我}{在}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 여기 있어요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>은행은 저기에 있어요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>어디 가세요?</t>
+  </si>
+  <si>
+    <r>
+      <t>얼화(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>儿</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>化):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 북방 지역에서는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(r)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>을 붙여 말하</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>去}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哪儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>银</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>行}{在}{那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/locatives/我在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/locatives/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>你去哪儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/locatives/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>银行在那儿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>demonstrative</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>这</t>
+  </si>
+  <si>
+    <t>那</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是}{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>狗</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이것은 개입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是狗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>狗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{那}{是}{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>牛肉}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource/video/那是牛肉.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>那是牛肉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저것은 소고기입니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -508,7 +1304,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -654,6 +1450,115 @@
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF57A64A"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="Microsoft YaHei"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="맑은 고딕 Semilight"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans KR"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -687,14 +1592,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -734,6 +1636,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1074,12 +1991,12 @@
   <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="64.75" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="87" bestFit="1" customWidth="1"/>
@@ -1091,29 +2008,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="4"/>
-      <c r="O1" s="4"/>
+      <c r="M1" s="3"/>
+      <c r="O1" s="3"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
@@ -1125,7 +2042,7 @@
       <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E2" t="s">
@@ -1134,12 +2051,12 @@
       <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="O2" s="5"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" ht="18">
       <c r="A3" t="s">
@@ -1163,8 +2080,8 @@
       <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
@@ -1176,7 +2093,7 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
@@ -1185,12 +2102,12 @@
       <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="5"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15" ht="18.75">
       <c r="A5" t="s">
@@ -1214,111 +2131,230 @@
       <c r="G5" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="O5" s="5"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="D6" s="6"/>
-      <c r="E6" s="2"/>
-      <c r="G6" s="5"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="O6" s="5"/>
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:15">
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="O7" s="5"/>
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="O8" s="5"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="1:15">
-      <c r="F9" s="5"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="O9" s="5"/>
+    <row r="9" spans="1:15" ht="18">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="O9" s="4"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="E10" s="2"/>
-      <c r="G10" s="5"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="O10" s="5"/>
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="O10" s="4"/>
     </row>
     <row r="11" spans="1:15">
       <c r="D11" s="1"/>
-      <c r="F11" s="5"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="O11" s="5"/>
+      <c r="F11" s="4"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="D12" s="11"/>
-      <c r="E12" s="3"/>
-      <c r="G12" s="5"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="2"/>
+      <c r="G12" s="4"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
     </row>
     <row r="13" spans="1:15">
-      <c r="D13" s="10"/>
-      <c r="F13" s="5"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
+      <c r="D13" s="9"/>
+      <c r="F13" s="4"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
     </row>
-    <row r="14" spans="1:15">
-      <c r="D14" s="7"/>
-      <c r="E14" s="2"/>
-      <c r="G14" s="5"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
+    <row r="14" spans="1:15" ht="18">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
     </row>
-    <row r="15" spans="1:15">
-      <c r="D15" s="6"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="5"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
+    <row r="15" spans="1:15" ht="18">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15">
+        <v>11</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="D16" s="7"/>
-      <c r="E16" s="2"/>
-      <c r="G16" s="5"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
     </row>
     <row r="17" spans="4:13">
-      <c r="D17" s="6"/>
-      <c r="F17" s="5"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
+      <c r="D17" s="5"/>
+      <c r="F17" s="4"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
     </row>
     <row r="18" spans="4:13">
-      <c r="D18" s="7"/>
-      <c r="E18" s="3"/>
-      <c r="G18" s="5"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="2"/>
+      <c r="G18" s="4"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
     </row>
     <row r="19" spans="4:13">
-      <c r="F19" s="5"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
+      <c r="F19" s="4"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
     </row>
     <row r="20" spans="4:13">
-      <c r="D20" s="8"/>
-      <c r="E20" s="9"/>
-      <c r="G20" s="5"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="8"/>
+      <c r="G20" s="4"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
     </row>
     <row r="21" spans="4:13">
-      <c r="F21" s="5"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
+      <c r="F21" s="4"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/resource/table/base_sentences.xlsx
+++ b/resource/table/base_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FC827B-2849-48A6-BCD7-EAE56EAEFA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4DFD76-1DAD-4DDE-9563-D22772528EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7035" yWindow="4110" windowWidth="27180" windowHeight="10935" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="78">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1076,12 +1076,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>这</t>
-  </si>
-  <si>
-    <t>那</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -1297,6 +1291,646 @@
   </si>
   <si>
     <t>저것은 소고기입니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : 이 (가까운 것을 가리킴)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>那 : 저 (멀리 있는 것)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{洗手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>在}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>里}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>화장실이 어디에 있나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/洗手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>间在哪里</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>洗手间在哪里</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>where</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/喜茶在几</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤이티는 몇 층에 있나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{喜茶}{在}{几}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>滩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这个</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>와이탄은 이 방향인가요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>滩是这个方向吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>外滩是这个方向吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">A + 是 + B + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>? : A는 B인가요?\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这个方向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> : 이 방향</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>在 (zài) : ~에 있다\n几</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ǐ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lóu) : 몇 층\n 几가 들어가서 '몇'이라는 의문문이 됨</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">} + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>哪里</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>? : {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>장소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가 어디에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있나요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>?\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>哪里</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가 들어가서 '어디'라는 의문문이 됨</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>喜茶在几楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1304,7 +1938,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="36">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1559,6 +2193,34 @@
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -1592,7 +2254,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1651,6 +2313,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1988,16 +2653,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC832AC-62FD-4F32-83D9-192679032F25}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="118.625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="87" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="36.75" bestFit="1" customWidth="1"/>
@@ -2200,19 +2865,19 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
         <v>54</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>55</v>
       </c>
-      <c r="E9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" t="s">
-        <v>52</v>
+      <c r="G9" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
@@ -2226,19 +2891,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
         <v>58</v>
       </c>
-      <c r="D10" t="s">
+      <c r="G10" t="s">
         <v>61</v>
-      </c>
-      <c r="E10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" t="s">
-        <v>53</v>
       </c>
       <c r="L10" s="12"/>
       <c r="M10" s="12"/>
@@ -2252,109 +2917,177 @@
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:15">
-      <c r="D12" s="10"/>
-      <c r="E12" s="2"/>
-      <c r="G12" s="4"/>
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>76</v>
+      </c>
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
     </row>
-    <row r="13" spans="1:15">
-      <c r="D13" s="9"/>
-      <c r="F13" s="4"/>
+    <row r="13" spans="1:15" ht="18.75">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s">
+        <v>75</v>
+      </c>
       <c r="L13" s="12"/>
       <c r="M13" s="12"/>
     </row>
-    <row r="14" spans="1:15" ht="18">
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>45</v>
+        <v>72</v>
+      </c>
+      <c r="F14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" t="s">
+        <v>74</v>
       </c>
       <c r="L14" s="12"/>
       <c r="M14" s="12"/>
     </row>
-    <row r="15" spans="1:15" ht="18">
-      <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15">
-        <v>11</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="18"/>
+    <row r="15" spans="1:15">
       <c r="L15" s="12"/>
       <c r="M15" s="12"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16">
-        <v>12</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="4"/>
       <c r="L16" s="12"/>
       <c r="M16" s="12"/>
     </row>
-    <row r="17" spans="4:13">
+    <row r="17" spans="1:13">
       <c r="D17" s="5"/>
       <c r="F17" s="4"/>
       <c r="L17" s="12"/>
       <c r="M17" s="12"/>
     </row>
-    <row r="18" spans="4:13">
+    <row r="18" spans="1:13">
       <c r="D18" s="6"/>
       <c r="E18" s="2"/>
       <c r="G18" s="4"/>
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
     </row>
-    <row r="19" spans="4:13">
+    <row r="19" spans="1:13">
       <c r="F19" s="4"/>
       <c r="L19" s="12"/>
       <c r="M19" s="12"/>
     </row>
-    <row r="20" spans="4:13">
+    <row r="20" spans="1:13">
       <c r="D20" s="7"/>
       <c r="E20" s="8"/>
       <c r="G20" s="4"/>
       <c r="L20" s="12"/>
       <c r="M20" s="12"/>
     </row>
-    <row r="21" spans="4:13">
+    <row r="21" spans="1:13">
       <c r="F21" s="4"/>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="D28" s="9"/>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:13" ht="18">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29">
+        <v>99</v>
+      </c>
+      <c r="C29" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="18">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30">
+        <v>100</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" t="s">
+        <v>50</v>
+      </c>
+      <c r="F30" s="18"/>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31">
+        <v>101</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="s">
+        <v>49</v>
+      </c>
+      <c r="G31" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/resource/table/base_sentences.xlsx
+++ b/resource/table/base_sentences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4DFD76-1DAD-4DDE-9563-D22772528EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CA4C6F-3EF9-4C15-8F29-81B32991D087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="83">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1931,6 +1931,49 @@
       </rPr>
       <t>.mp3</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{能不能}{便宜}{一点}?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조금만 싸게 해주실 수 있나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource/video/能不能便宜一点.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>能不能便宜一点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>discount</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3018,8 +3061,24 @@
       <c r="M19" s="12"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20">
+        <v>98</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" t="s">
+        <v>81</v>
+      </c>
       <c r="G20" s="4"/>
       <c r="L20" s="12"/>
       <c r="M20" s="12"/>

--- a/resource/table/base_sentences.xlsx
+++ b/resource/table/base_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CA4C6F-3EF9-4C15-8F29-81B32991D087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04B0DE8-FD41-41E4-BF6C-BC65D9A5E6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="93">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1974,6 +1974,309 @@
   </si>
   <si>
     <t>discount</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hair</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 장원영 같은 헤어스타일로 자르고 싶어요</t>
+  </si>
+  <si>
+    <r>
+      <t>我想 + 동사 : 나는 ~ 하고싶다\n  A那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>样的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>B : “A 같은 B” \n 那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>样</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>+的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 그런식 + 의</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/我想剪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>张元英那样的发型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我想剪张元英那样的发型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{我}{想}{剪}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>张元英</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{那</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>样</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{的}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{水</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>温</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>有点}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>烫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>수온이 조금 뜨거워요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有点 : 약간, 조금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/水</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>温</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>有点</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>烫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1981,7 +2284,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="40">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2027,13 +2330,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF57A64A"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFB5CEA8"/>
       <name val="Consolas"/>
       <family val="3"/>
@@ -2057,13 +2353,6 @@
       <color rgb="FF4EC9B0"/>
       <name val="Consolas"/>
       <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF57A64A"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2297,17 +2586,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2316,16 +2608,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2334,19 +2617,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2355,10 +2641,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2701,8 +2984,8 @@
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="48.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="118.625" bestFit="1" customWidth="1"/>
@@ -2716,22 +2999,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -2759,11 +3042,11 @@
       <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" ht="18">
@@ -2788,8 +3071,8 @@
       <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
@@ -2801,7 +3084,7 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
@@ -2810,11 +3093,11 @@
       <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15" ht="18.75">
@@ -2839,8 +3122,8 @@
       <c r="G5" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
       <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15">
@@ -2850,10 +3133,10 @@
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="13" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
@@ -2862,11 +3145,11 @@
       <c r="F6" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
       <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:15">
@@ -2888,16 +3171,16 @@
       <c r="F7" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
       <c r="O8" s="4"/>
     </row>
     <row r="9" spans="1:15" ht="18">
@@ -2919,11 +3202,11 @@
       <c r="F9" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
       <c r="O9" s="4"/>
     </row>
     <row r="10" spans="1:15">
@@ -2948,15 +3231,15 @@
       <c r="G10" t="s">
         <v>61</v>
       </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
       <c r="O10" s="4"/>
     </row>
     <row r="11" spans="1:15">
       <c r="D11" s="1"/>
       <c r="F11" s="4"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:15">
@@ -2969,7 +3252,7 @@
       <c r="C12" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="8" t="s">
         <v>63</v>
       </c>
       <c r="E12" t="s">
@@ -2978,11 +3261,11 @@
       <c r="F12" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
     </row>
     <row r="13" spans="1:15" ht="18.75">
       <c r="A13" t="s">
@@ -3006,8 +3289,8 @@
       <c r="G13" t="s">
         <v>75</v>
       </c>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
@@ -3031,66 +3314,104 @@
       <c r="G14" t="s">
         <v>74</v>
       </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
+      <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" t="s">
+        <v>85</v>
+      </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
     </row>
-    <row r="17" spans="1:13">
-      <c r="D17" s="5"/>
-      <c r="F17" s="4"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
+    <row r="17" spans="1:13" ht="18.75">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" t="s">
+        <v>91</v>
+      </c>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="D18" s="6"/>
+      <c r="D18" s="5"/>
       <c r="E18" s="2"/>
       <c r="G18" s="4"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
     </row>
     <row r="19" spans="1:13">
       <c r="F19" s="4"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20">
-        <v>98</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" t="s">
-        <v>81</v>
-      </c>
       <c r="G20" s="4"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
     </row>
     <row r="21" spans="1:13">
       <c r="F21" s="4"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="D28" s="9"/>
-      <c r="F28" s="4"/>
+      <c r="A28" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28">
+        <v>98</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="29" spans="1:13" ht="18">
       <c r="A29" t="s">
@@ -3108,7 +3429,7 @@
       <c r="E29" t="s">
         <v>48</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="17" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3119,7 +3440,7 @@
       <c r="B30">
         <v>100</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>47</v>
       </c>
       <c r="D30" t="s">
@@ -3128,7 +3449,7 @@
       <c r="E30" t="s">
         <v>50</v>
       </c>
-      <c r="F30" s="18"/>
+      <c r="F30" s="16"/>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
@@ -3137,7 +3458,7 @@
       <c r="B31">
         <v>101</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D31" t="s">

--- a/resource/table/base_sentences.xlsx
+++ b/resource/table/base_sentences.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D04B0DE8-FD41-41E4-BF6C-BC65D9A5E6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2419A9D-F4BA-4318-843E-20711B9B4164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="94">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -450,60 +450,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>resource/video/fruit_store/我要</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>两斤草莓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/video/fruit_store/苹果多少</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>钱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>shi</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2277,6 +2223,64 @@
       </rPr>
       <t>.mp4</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/苹果多少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/我要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>两斤草莓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>test</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2979,7 +2983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC832AC-62FD-4F32-83D9-192679032F25}">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
@@ -3037,7 +3041,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -3063,7 +3067,7 @@
         <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
@@ -3128,25 +3132,25 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>33</v>
       </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
       <c r="G6" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
@@ -3154,25 +3158,25 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
       <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>39</v>
       </c>
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
@@ -3185,25 +3189,25 @@
     </row>
     <row r="9" spans="1:15" ht="18">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9">
         <v>7</v>
       </c>
       <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
         <v>52</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>53</v>
       </c>
-      <c r="E9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
       <c r="G9" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
@@ -3211,25 +3215,25 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B10">
         <v>8</v>
       </c>
       <c r="C10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
         <v>56</v>
       </c>
-      <c r="D10" t="s">
+      <c r="G10" t="s">
         <v>59</v>
-      </c>
-      <c r="E10" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" t="s">
-        <v>61</v>
       </c>
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
@@ -3244,75 +3248,75 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B12">
         <v>9</v>
       </c>
       <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="F12" t="s">
         <v>63</v>
       </c>
-      <c r="E12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
       <c r="G12" s="18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
     </row>
     <row r="13" spans="1:15" ht="18.75">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B13">
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B14">
         <v>11</v>
       </c>
       <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" t="s">
         <v>70</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>71</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>72</v>
-      </c>
-      <c r="F14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G14" t="s">
-        <v>74</v>
       </c>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
@@ -3323,50 +3327,50 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B16">
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" t="s">
         <v>84</v>
       </c>
-      <c r="E16" t="s">
-        <v>86</v>
-      </c>
       <c r="F16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
     </row>
     <row r="17" spans="1:13" ht="18.75">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B17">
         <v>13</v>
       </c>
       <c r="C17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" t="s">
         <v>89</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" t="s">
-        <v>91</v>
       </c>
       <c r="L17" s="10"/>
       <c r="M17" s="10"/>
@@ -3395,79 +3399,125 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B28">
         <v>98</v>
       </c>
       <c r="C28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="F28" t="s">
         <v>79</v>
-      </c>
-      <c r="E28" t="s">
-        <v>80</v>
-      </c>
-      <c r="F28" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="18">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B29">
         <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="18">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>100</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F30" s="16"/>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B31">
         <v>101</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G31" s="4"/>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35">
+        <v>998</v>
+      </c>
+      <c r="C35" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" t="s">
+        <v>91</v>
+      </c>
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36">
+        <v>999</v>
+      </c>
+      <c r="C36" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" t="s">
+        <v>91</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/resource/table/base_sentences.xlsx
+++ b/resource/table/base_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2419A9D-F4BA-4318-843E-20711B9B4164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FCDCA2-872D-45A7-9C87-9D564CC35953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="1500" yWindow="2040" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/resource/table/base_sentences.xlsx
+++ b/resource/table/base_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FCDCA2-872D-45A7-9C87-9D564CC35953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4246A33-6CE0-4A33-A24D-E44C3DA24D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="2040" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="95">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2281,6 +2281,33 @@
   </si>
   <si>
     <t>test</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>水温有点烫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2288,7 +2315,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="38">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2357,13 +2384,6 @@
       <color rgb="FF4EC9B0"/>
       <name val="Consolas"/>
       <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF57A64A"/>
-      <name val="Consolas"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2590,7 +2610,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2609,9 +2629,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2621,13 +2638,16 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2636,16 +2656,13 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3003,22 +3020,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -3046,11 +3063,11 @@
       <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" ht="18">
@@ -3075,8 +3092,8 @@
       <c r="G3" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
@@ -3088,7 +3105,7 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
@@ -3097,11 +3114,11 @@
       <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15" ht="18.75">
@@ -3126,8 +3143,8 @@
       <c r="G5" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
       <c r="O5" s="4"/>
     </row>
     <row r="6" spans="1:15">
@@ -3137,10 +3154,10 @@
       <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>28</v>
       </c>
       <c r="E6" t="s">
@@ -3149,11 +3166,11 @@
       <c r="F6" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
       <c r="O6" s="4"/>
     </row>
     <row r="7" spans="1:15">
@@ -3175,16 +3192,16 @@
       <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
       <c r="O7" s="4"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
       <c r="O8" s="4"/>
     </row>
     <row r="9" spans="1:15" ht="18">
@@ -3206,11 +3223,11 @@
       <c r="F9" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
       <c r="O9" s="4"/>
     </row>
     <row r="10" spans="1:15">
@@ -3235,15 +3252,15 @@
       <c r="G10" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
       <c r="O10" s="4"/>
     </row>
     <row r="11" spans="1:15">
       <c r="D11" s="1"/>
       <c r="F11" s="4"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
       <c r="O11" s="4"/>
     </row>
     <row r="12" spans="1:15">
@@ -3256,7 +3273,7 @@
       <c r="C12" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>61</v>
       </c>
       <c r="E12" t="s">
@@ -3265,11 +3282,11 @@
       <c r="F12" t="s">
         <v>63</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
     </row>
     <row r="13" spans="1:15" ht="18.75">
       <c r="A13" t="s">
@@ -3293,8 +3310,8 @@
       <c r="G13" t="s">
         <v>73</v>
       </c>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
@@ -3318,37 +3335,16 @@
       <c r="G14" t="s">
         <v>72</v>
       </c>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
     </row>
     <row r="15" spans="1:15">
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F16" t="s">
-        <v>85</v>
-      </c>
-      <c r="G16" t="s">
-        <v>83</v>
-      </c>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
     </row>
     <row r="17" spans="1:13" ht="18.75">
       <c r="A17" t="s">
@@ -3360,42 +3356,60 @@
       <c r="C17" t="s">
         <v>87</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="12" t="s">
         <v>88</v>
       </c>
       <c r="E17" t="s">
         <v>90</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G17" t="s">
         <v>89</v>
       </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
     </row>
     <row r="18" spans="1:13">
-      <c r="D18" s="5"/>
-      <c r="E18" s="2"/>
-      <c r="G18" s="4"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
+      <c r="A18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" t="s">
+        <v>83</v>
+      </c>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
     </row>
     <row r="19" spans="1:13">
       <c r="F19" s="4"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
     </row>
     <row r="20" spans="1:13">
       <c r="G20" s="4"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
     </row>
     <row r="21" spans="1:13">
       <c r="F21" s="4"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
@@ -3407,7 +3421,7 @@
       <c r="C28" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>77</v>
       </c>
       <c r="E28" t="s">
@@ -3433,7 +3447,7 @@
       <c r="E29" t="s">
         <v>46</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" s="16" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3444,7 +3458,7 @@
       <c r="B30">
         <v>100</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D30" t="s">
@@ -3453,7 +3467,7 @@
       <c r="E30" t="s">
         <v>48</v>
       </c>
-      <c r="F30" s="16"/>
+      <c r="F30" s="15"/>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
@@ -3462,7 +3476,7 @@
       <c r="B31">
         <v>101</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D31" t="s">
@@ -3492,7 +3506,7 @@
       <c r="F35" t="s">
         <v>10</v>
       </c>
-      <c r="G35" s="11" t="s">
+      <c r="G35" s="10" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3515,7 +3529,7 @@
       <c r="F36" t="s">
         <v>10</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="10" t="s">
         <v>23</v>
       </c>
     </row>

--- a/resource/table/base_sentences.xlsx
+++ b/resource/table/base_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4246A33-6CE0-4A33-A24D-E44C3DA24D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECBA4C77-EA2B-49B8-8B45-90E1C7A6D250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-35820" yWindow="1800" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="111">
   <si>
     <t>topic</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2296,6 +2296,549 @@
         <charset val="134"/>
       </rPr>
       <t>水温有点烫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>restaurant</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>고수 빼주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{不}{要}{香菜}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>종업원님, 얼음물 좀 주세요</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource/video/不要香菜.mp4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不要香菜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/服</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>务员请给我冰水</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{服</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>务员</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>},{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}{我}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{冰水}</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/老板可以刷卡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>{老板},{可以}{刷}{卡}{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei UI"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>？</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>사장님, 카드 결제 되나요?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">不 (bù) : 아니다, 안 하다 (Not)\n要 (yào) : 원하다, 필요로 하다 (Want / Need) </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ǐ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ng) : ~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>주세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Please)\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (gěi) : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Give)\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>我</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (wǒ) : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>나</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Me)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>可以(k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ě</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ǐ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) : ~할 수 있다\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (ma) : ~인가요?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>服务员,请给我冰水</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>老板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可以刷卡吗</t>
     </r>
     <r>
       <rPr>
@@ -2315,7 +2858,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2578,6 +3121,19 @@
       <name val="Consolas"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3407,9 +3963,75 @@
       <c r="M20" s="9"/>
     </row>
     <row r="21" spans="1:13">
-      <c r="F21" s="4"/>
+      <c r="A21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" t="s">
+        <v>100</v>
+      </c>
+      <c r="G21" t="s">
+        <v>106</v>
+      </c>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
+    </row>
+    <row r="22" spans="1:13" ht="18">
+      <c r="A22" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">

--- a/resource/table/base_sentences.xlsx
+++ b/resource/table/base_sentences.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECBA4C77-EA2B-49B8-8B45-90E1C7A6D250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9602B957-E2F4-453F-B5E4-3B7E65909B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35820" yWindow="1800" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2531,7 +2531,150 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">不 (bù) : 아니다, 안 하다 (Not)\n要 (yào) : 원하다, 필요로 하다 (Want / Need) </t>
+    <r>
+      <t>可以(k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ě</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>ǐ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) : ~할 수 있다\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (ma) : ~인가요?</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>服务员,请给我冰水</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/sound/sentense/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>老板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可以刷卡吗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不 (bù) : 아니다\n要 (yào) : 원하다, 필요로 하다</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2611,7 +2754,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (Please)\n</t>
+      <t>\n</t>
     </r>
     <r>
       <rPr>
@@ -2649,7 +2792,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> (Give)\n</t>
+      <t>\n</t>
     </r>
     <r>
       <rPr>
@@ -2679,177 +2822,6 @@
         <charset val="129"/>
       </rPr>
       <t>나</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>저</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Me)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>可以(k</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="238"/>
-      </rPr>
-      <t>ě</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>y</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI"/>
-        <family val="2"/>
-        <charset val="238"/>
-      </rPr>
-      <t>ǐ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) : ~할 수 있다\n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>吗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (ma) : ~인가요?</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/sound/sentense/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>服务员,请给我冰水</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp3</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/sound/sentense/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>老板</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>可以刷卡吗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp3</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3982,7 +3954,7 @@
         <v>100</v>
       </c>
       <c r="G21" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
@@ -4004,10 +3976,10 @@
         <v>101</v>
       </c>
       <c r="F22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -4027,10 +3999,10 @@
         <v>103</v>
       </c>
       <c r="F23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G23" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:13">

--- a/resource/table/base_sentences.xlsx
+++ b/resource/table/base_sentences.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,8 +454,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -489,8 +491,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -524,8 +528,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -559,8 +565,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -594,8 +602,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -629,8 +639,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -673,8 +685,10 @@
       <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -708,8 +722,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -752,8 +768,10 @@
       <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>9</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -787,8 +805,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>10</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -822,8 +842,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>11</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -875,8 +897,10 @@
       <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>13</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -910,8 +934,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>14</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -963,8 +989,10 @@
       <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>15</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -998,8 +1026,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>16</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1033,8 +1063,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>17</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1105,8 +1137,10 @@
       <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>98</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1136,8 +1170,10 @@
       <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>99</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1167,8 +1203,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>100</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1194,8 +1232,10 @@
       <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>101</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1248,8 +1288,10 @@
       <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>998</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1283,8 +1325,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>999</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1314,6 +1358,45 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>多少(얼마)\n 多少+钱(돈) : 가격을 묻는 표현</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>taxi</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>{我们}{打车}{去}{吧}</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>우리 택시 타고 가자</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>resource/video/我们打车去吧.mp4</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>resource/sound/sentense/我们打车去吧.mp3</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>打车 : 택시를 타다
+去 : 가다
+吧 : ~하자 ( 제안 )</t>
         </is>
       </c>
     </row>
